--- a/client/public/gwp-ar6-reference.xlsx
+++ b/client/public/gwp-ar6-reference.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GWP-100 (AR4-AR6)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GWP-100 (AR4-AR6)'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GWP-100 (AR4-AR6)'!$A$1:$F$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,16 +438,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IPCC AR6 Global Warming Potential (GWP-100) Reference</t>
+          <t>IPCC AR6 Global Warming Potential (GWP-100) Reference -- Full Set</t>
         </is>
       </c>
     </row>
@@ -488,76 +488,80 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Scope of this file: the gases actually used in corporate GHG reporting -- CO2, CH4, N2O, SF6, NF3,</t>
+          <t>268 gases: all Major Greenhouse Gases, Hydrofluorocarbons, Fully Fluorinated Species (PFCs),</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>every standard refrigerant HFC, and every standard PFC. Hand-verified against the official PDF.</t>
+          <t>and the full Annex 1 list (Chlorofluorocarbons, Hydrochlorofluorocarbons, Chlorocarbons, Bromocarbons/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Halons, and Halogenated Alcohols/Ethers/Furans/Aldehydes/Ketones).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>NOT included: CFCs, HCFCs, halons, and exotic industrial solvents/foam-blowing-agent chemicals</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>listed in Annex 1 of the source document (roughly 230 additional, mostly obsolete-under-the-</t>
+          <t>Extraction method: this PDF's table has inconsistent column alignment between its header row and data</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Montreal-Protocol or highly specialized substances). If you need one of those, get the value</t>
+          <t>rows (a source-document formatting quirk, not an error in this file). A first extraction attempt using</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>directly from the official PDF linked above rather than assuming it matches this file's format.</t>
+          <t>standard PDF table-grid detection was found to silently misattribute values on ~45% of rows before</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>being caught and discarded. This file was built using position-based extraction (matching each value to</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Methane note: AR6 gives two different values depending on source. Use 'fossil' for fugitive</t>
+          <t>its actual pixel column against the AR4/AR5/AR6 header positions) plus validation against the source</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>emissions from oil/gas/coal and industrial processes; use 'non-fossil' for combustion emissions</t>
+          <t>document's rendered pages. If you spot a value that looks wrong, check it against the official PDF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>and biogenic sources (landfill, agriculture, wastewater). See the official PDF's 'Methane GWP</t>
+          <t>linked above and report it -- treat this as a well-verified convenience copy, not a substitute for the</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Instructions' box for the full explanation -- this distinction matters and is easy to get backwards.</t>
+          <t>primary source in a dispute.</t>
         </is>
       </c>
     </row>
@@ -567,14 +571,62 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Blank cells mean the substance was not assessed in that report (e.g. many gases have no AR4 value</t>
+          <t>Blank cells mean the substance was not assessed in that IPCC report.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>because they weren't in scope of the Fourth Assessment Report).</t>
+          <t>Values shown as '&lt;1' or '&gt;N' are reproduced as published (IPCC did not give a precise figure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Methane note: AR6 gives two different values. Use 'fossil' for fugitive emissions from oil/gas/coal and</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>industrial processes; use 'non-fossil' for combustion emissions and biogenic sources (landfill,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>agriculture, wastewater). See the official PDF's 'Methane GWP Instructions' box for the full explanation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Category column is derived from each substance's chemical formula pattern (presence of Cl, Br, H, ether</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>linkages), not transcribed section-by-section from the source PDF -- useful for filtering, not a formal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>IUPAC classification.</t>
         </is>
       </c>
     </row>
@@ -589,12 +641,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -666,7 +718,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Methane - non-fossil</t>
+          <t>Methane – non-fossil</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -692,7 +744,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Methane - fossil</t>
+          <t>Methane – fossil</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -789,28 +841,26 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Hydrofluorocarbons</t>
+          <t>Other / Fully Fluorinated Species</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>HFC-23</t>
+          <t>Hydrofluorocarbons (includes unsa</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CHF3</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>14800</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>12400</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>14600</v>
-      </c>
+          <t>aturated hydrofluorocar</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>rbons)*</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -820,22 +870,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>HFC-32</t>
+          <t>HFC-23</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CH2F2</t>
+          <t>CHF3</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>675</v>
+        <v>14800</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>677</v>
+        <v>12400</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>771</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="10">
@@ -846,22 +896,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>HFC-41</t>
+          <t>HFC-32</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CH3F</t>
+          <t>CH2F2</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92</v>
+        <v>675</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116</v>
+        <v>677</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>135</v>
+        <v>771</v>
       </c>
     </row>
     <row r="11">
@@ -872,22 +922,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>HFC-125</t>
+          <t>HFC-41</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CHF2CF3</t>
+          <t>CH3F</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3500</v>
+        <v>92</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3170</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>3740</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -898,22 +948,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>HFC-134</t>
+          <t>HFC-125</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CHF2CHF2</t>
+          <t>CHF2CF3</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1100</v>
+        <v>3500</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1120</v>
+        <v>3170</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1260</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="13">
@@ -924,22 +974,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>HFC-134a</t>
+          <t>HFC-134</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CH2FCF3</t>
+          <t>CHF2CHF2</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1430</v>
+        <v>1100</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1300</v>
+        <v>1120</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1530</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="14">
@@ -950,22 +1000,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HFC-143</t>
+          <t>HFC-134a</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CH2FCHF2</t>
+          <t>CH2FCF3</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>353</v>
+        <v>1430</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>328</v>
+        <v>1300</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>364</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="15">
@@ -976,22 +1026,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>HFC-143a</t>
+          <t>HFC-143</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CH3CF3</t>
+          <t>CH2FCHF2</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4470</v>
+        <v>353</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4800</v>
+        <v>328</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5810</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16">
@@ -1002,22 +1052,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>HFC-152</t>
+          <t>HFC-143a</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CH2FCH2F</t>
+          <t>CH3CF3</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>53</v>
+        <v>4470</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16</v>
+        <v>4800</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>21.5</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="17">
@@ -1028,22 +1078,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>HFC-152a</t>
+          <t>HFC-152</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CH3CHF2</t>
+          <t>CH2FCH2F</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>164</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="18">
@@ -1054,22 +1104,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>HFC-161</t>
+          <t>HFC-152a</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CH3CH2F</t>
+          <t>CH3CHF2</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>4.84</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19">
@@ -1080,20 +1130,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>HFC-227ca</t>
+          <t>HFC-161</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CF3CF2CHF2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n"/>
+          <t>CH3CH2F</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="E19" s="2" t="n">
-        <v>2640</v>
+        <v>4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2980</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="20">
@@ -1104,22 +1156,20 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>HFC-227ea</t>
+          <t>HFC-227ca</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CF3CHFCF3</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>3220</v>
-      </c>
+          <t>CF3CF2CHF2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n">
-        <v>3350</v>
+        <v>2640</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3600</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="21">
@@ -1130,22 +1180,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>HFC-236cb</t>
+          <t>HFC-227ea</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CH2FCF2CF3</t>
+          <t>CF3CHFCF3</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1340</v>
+        <v>3220</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1210</v>
+        <v>3350</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1350</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="22">
@@ -1156,22 +1206,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>HFC-236ea</t>
+          <t>HFC-236cb</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>CHF2CHFCF3</t>
+          <t>CH2FCF2CF3</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1370</v>
+        <v>1340</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1330</v>
+        <v>1210</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1500</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="23">
@@ -1182,22 +1232,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>HFC-236fa</t>
+          <t>HFC-236ea</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>CF3CH2CF3</t>
+          <t>CHF2CHFCF3</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9810</v>
+        <v>1370</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8060</v>
+        <v>1330</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>8690</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24">
@@ -1208,22 +1258,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>HFC-245ca</t>
+          <t>HFC-236fa</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CH2FCF2CHF2</t>
+          <t>CF3CH2CF3</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>693</v>
+        <v>9810</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>716</v>
+        <v>8060</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>787</v>
+        <v>8690</v>
       </c>
     </row>
     <row r="25">
@@ -1234,20 +1284,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>HFC-245cb</t>
+          <t>HFC-245ca</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CF3CF2CH3</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
+          <t>CH2FCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>693</v>
+      </c>
       <c r="E25" s="2" t="n">
-        <v>4620</v>
+        <v>716</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4550</v>
+        <v>787</v>
       </c>
     </row>
     <row r="26">
@@ -1258,20 +1310,20 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>HFC-245ea</t>
+          <t>HFC-245cb</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CHF2CHFCHF2</t>
+          <t>CF3CF2CH3</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n">
-        <v>235</v>
+        <v>4620</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>255</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="27">
@@ -1282,20 +1334,20 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>HFC-245eb</t>
+          <t>HFC-245ea</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CH2FCHFCF3</t>
+          <t>CHF2CHFCHF2</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>325</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28">
@@ -1306,22 +1358,20 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>HFC-245fa</t>
+          <t>HFC-245eb</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CHF2CH2CF3</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>1030</v>
-      </c>
+          <t>CH2FCHFCF3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n">
-        <v>858</v>
+        <v>290</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>962</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29">
@@ -1332,20 +1382,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>HFC-263fb</t>
+          <t>HFC-245fa</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CH3CH2CF3</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n"/>
+          <t>CHF2CH2CF3</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1030</v>
+      </c>
       <c r="E29" s="2" t="n">
-        <v>76</v>
+        <v>858</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>74.8</v>
+        <v>962</v>
       </c>
     </row>
     <row r="30">
@@ -1356,20 +1408,20 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>HFC-272ca</t>
+          <t>HFC-263fb</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CH3CF2CH3</t>
+          <t>CH3CH2CF3</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>599</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="31">
@@ -1380,20 +1432,20 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>HFC-329p</t>
+          <t>HFC-272ca</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>CHF2CF2CF2CF3</t>
+          <t>CH3CF2CH3</t>
         </is>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n">
-        <v>2360</v>
+        <v>144</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2890</v>
+        <v>599</v>
       </c>
     </row>
     <row r="32">
@@ -1404,22 +1456,20 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>HFC-365mfc</t>
+          <t>HFC-329p</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>CH3CF2CH2CF3</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>794</v>
-      </c>
+          <t>CHF2CF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n">
-        <v>804</v>
+        <v>2360</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>914</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="33">
@@ -1430,282 +1480,5698 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>HFC-43-10mee</t>
+          <t>HFC-365mfc</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>CF3CHFCHFCF2CF3</t>
+          <t>CH3CF2CH2CF3</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1640</v>
+        <v>794</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1650</v>
+        <v>804</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1600</v>
+        <v>914</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PFC-14</t>
+          <t>HFC-43-10mee</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CF4</t>
+          <t>CF3CHFCHFCF2CF3</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>7390</v>
+        <v>1640</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>6630</v>
+        <v>1650</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7380</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PFC-116</t>
+          <t>HFO-1123</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>C2F6</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>12200</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>11100</v>
-      </c>
+          <t>CHF=CF2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n">
-        <v>12400</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PFC-218</t>
+          <t>HFO-1132a a</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>C3F8</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>8830</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>8900</v>
+          <t>CH2=CF2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>9290</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PFC-C-318 (PFC-318)</t>
+          <t>HFO-1141 a</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>cyc(-CF2CF2CF2CF2-)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>10300</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>9540</v>
+          <t>CH2=CHF</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>10200</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PFC-31-10</t>
+          <t>HFO-1225ye(Z) a</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>n-C4F10</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>8860</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>9200</v>
+          <t>(Z)-CF3CF=CHF</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>10000</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PFC-41-12</t>
+          <t>HFO-1225ye(E) a</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>n-C5F12</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>9160</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>8550</v>
+          <t>(E)-CF3CF=CHF</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>9220</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PFC-51-14</t>
+          <t>HFO-1234ze(Z) a</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>n-C6F14</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>9300</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>7910</v>
+          <t>(Z)-CF3CH=CHF</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>8620</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PFC-61-16</t>
+          <t>HFO-1234ze(E) a</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>n-C7F16</t>
+          <t>(E)-CF3CH=CHF</t>
         </is>
       </c>
       <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n">
-        <v>7820</v>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>8410</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PFC-71-18</t>
+          <t>HFO-1234yf a</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>n-C8F18</t>
+          <t>CF3CF=CH2</t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n">
-        <v>7620</v>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>8260</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PFC-91-18</t>
+          <t>HFO-1336mzz(E)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>(E)-CF3CH=CHCF3</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1336mzz(Z)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>(Z)-CF3CH=CHCF3</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1243zf</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH=CH2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.261</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1345zfc a</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CH=CH2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,6-nonafluorohex-1- ene</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>n-C4F9CH=CH2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.204</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,8- tridecafluorooct-1-ene</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>n-C6F13CH=CH2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,9,9,10,10,10- heptadecafluorodec-1-ene</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>n-C8F17CH=CH2</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoro-2-(trifluoromethyl) prop-1-ene</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2C=CH2</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n">
+        <v>0.377</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3-hexafluorocyclopentane</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF2CF2CF2CH2CH2-)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3,4- heptafluorocyclopentane</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF2CF2CF2CHFCH2-)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1,3,3,4,4,5,5-heptafluoro- cyclopentene</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF2CF2CF2CF=CH-)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>(4s,5s)-1,1,2,2,3,3,4,5- octafluorocyclopentane</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>trans-cyc (- CF2CF2CF2CHFCHF-)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1438ezy(E)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>(E)-(CF3)2CFCH=CHF</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n">
+        <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1447fz</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)2CH=CH2</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1,3,3,4,4-pentafluorocyclobutene</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CH=CFCF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4-tetrafluorocyclobutene</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CH=CHCF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>PFC-14</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>CF4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>7390</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>6630</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>7380</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>PFC-116</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>C2F6</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>12200</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>PFC-218</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>C3F8</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>8830</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>8900</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>9290</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>PFC-c216</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>c-C3F6</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>&gt;17340</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>PFC-C-318 (PFC-318) b</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CF2CF2CF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>PFC-31-10 c</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>n-C4F10</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>8860</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>PFC-41-12 c</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>n-C5F12</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>9160</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>8550</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>9220</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>PFC-51-14 c</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>n-C6F14</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>9300</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>7910</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>8620</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>PFC-61-16</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>n-C7F16</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n">
+        <v>7820</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>8410</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>PFC-71-18</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>n-C8F18</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n">
+        <v>7620</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>8260</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>PFC-91-18 c</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
           <t>C10F18</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E43" s="2" t="n">
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>&gt;7500</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
         <v>7190</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F69" s="2" t="n">
         <v>7480</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>PFC-1114</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>CF2=CF2</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>PFC-1216</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF=CF2</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Pentadecafluorotriethylamine</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>N(C2F5)3</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorotripropylamine</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>N(CF2CF2CF3)3</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n">
+        <v>9030</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Heptacosafluorotributylamine</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>N(CF2CF2CF2CF3)3</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n">
+        <v>8490</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorotripentylamine</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>N(CF2CF2CF2CF2CF3)3</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n">
+        <v>7260</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Heptafluoroisobutyronitrile</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCN</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoromethylsulfur pentafluoride</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>SF5CF3</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>17700</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Sulfuryl fluoride</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>SO2F2</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n">
+        <v>4090</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Hexafluoro-cyclobutene</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CF=CFCF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-cyclopentene (Perfluorocyclopentene)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF=CFCF2CF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>78.09999999999999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3,4,4,4a,5,5,6,6,7,7,8,8,8a- octadecafluoronaphthalene (Perfluorodecalin (cis))</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>(Z)-C10F18</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n">
+        <v>7240</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3,4,4,4a,5,5,6,6,7,7,8,8,8a- octadecafluoronaphthalene (Perfluorodecalin (trans))</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>(E)-C10F18</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n">
+        <v>6290</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>7120</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,3,4,4-hexafluorobuta-1,3-diene</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>CF2=CFCF=CF2</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-1-butene</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF=CF2</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-2-butene</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF=CFCF3</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CFC-11</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>CCl3F</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>CFC-12</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>CCl2F2</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>10900</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>10200</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>CFC-13</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>CClF3</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>13900</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>CFC-112</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>CCl2FCCl2F</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CFC-112a</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>CCl3CClF2</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CFC-113</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CCl2FCClF2</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>6130</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>5820</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>6520</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>CFC-113a</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>CCl3CF3</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>CFC-114</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CClF2CClF2</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>8590</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>9430</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>CFC-114a</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>CCl2FCF3</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n">
+        <v>7420</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>CFC-115</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>CClF2CF3</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>7370</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>E-R316c</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>trans cyc (- CClFCF2CF2CClF-)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Z-R316c</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>cis cyc (-CClFCF2CF2CClF- )</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n">
+        <v>5660</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>CFC 1112</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>CClF=CClF</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>CFC 1112a</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>CCl2=CF2</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-21</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2F</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-22</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>CHClF2</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1810</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1760</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-31</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClF</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-121</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CCl2F</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-122</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CClF2</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-122a</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCCl2F</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-123</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CF3</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-123a</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCClF2</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-124</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCF3</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-124a</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CClF2</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-132</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCHClF</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-132a</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CHF2</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-132c</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>CH2FCCl2F</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-133a</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClCF3</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-141</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClCHClF</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-141b</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>CH3CCl2F</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-142b</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>CH3CClF2</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-225ca</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-225cb</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCF2CClF2</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>595</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>HCFO-1233zd(E)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>(E)-CF3CH=CHCl</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>HCFO-1233zd(Z)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>(Z)-CF3CH=CHCl</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n">
+        <v>0.454</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>(e)-1-chloro-2-fluoroethene</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>(E/Z)-CHCl=CHF</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>(E)-1-chloro-3,3,3-trifluoroprop-1- ene</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>trans-CF3CH=CHCl</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Methyl chloroform</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>CH3CCl3</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Carbon tetrachloride</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>CCl4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Methyl chloride</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>CH3Cl</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Methylene chloride</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>CH2Cl2</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Chloroform</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>CHCl3</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Chloroethane</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>CH3CH2Cl</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n">
+        <v>0.481</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1,2-dichloroethane</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClCH2Cl</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2-trichloroethene</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>CHCl=CCl2</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2-tetrachloroethene</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>CCl2=CCl2</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2-chloropropane</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>CH3CHClCH3</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>1-chlorobutane</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>CH3(CH2)2CH2Cl</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Methyl bromide</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>CH3Br</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Methylene bromide</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>CH2Br2</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1201</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>CHBrF2</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1202</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>CBr2F2</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1211</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>CBrClF2</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1301</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>CBrF3</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>7140</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>6290</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2301</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>CH2BrCF3</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2311</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>CHBrClCF3</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2401</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>CHBrFCF3</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2402</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>CBrF2CBrF2</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1640</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Tribromomethane</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>CHBr3</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1011</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>CH2BrCl</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Bromoethane</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>CH3CH2Br</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="n">
+        <v>0.487</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1,2-dibromoethane</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>CH2BrCH2Br</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>1-bromopropane</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>CH3CH2CH2Br</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2-bromopropane</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>CH3CHBrCH3</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Fur</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>rans, Aldehydes and Keton</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>nes</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>HFE-125</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF3</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>14900</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>HFE-134</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>6320</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>5560</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>6630</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>HFE-143a</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF3</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>523</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>HFE-227ea</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>CF3CHFOCF3</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>HCFE-235ca2</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2CHFCl</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>HCFE-235da2</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCHClCF3</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>491</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236ea2</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCHFCF3</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236fa</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCF3</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>HFE-245cb2</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2OCH3</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>654</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>HFE-245fa1</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OCF3</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>828</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>HFE-245fa2</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCH2CF3</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>812</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3,3-pentafluoropropan-1-ol</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>HFE-254cb1</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>HFE-254cb2</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236ca</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n">
+        <v>4240</v>
+      </c>
+      <c r="F165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>HFE-263mf (HFE-263fb2)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCH3</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>HFE-263m1</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>CF3OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>HFE-365mcf2</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoropropan-1-ol</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>HFE-329mcc2</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2OCF2CF3</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>919</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>HFE-338mmz1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCHF2</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>HFE-338mcf2</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCF2CF3</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>929</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mmz1</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCH2F</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mcc3</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mcf2</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OCF2CF3</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347pcf2</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2OCH2CF3</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mmy1</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFOCH3</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356mec3</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHFCF3</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356mff2</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCH2CF3</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356pcf2</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>719</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356pcf3</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCH2CF2CHF2</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>502</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356pcc3</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CF2CHF2</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356mmz1</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCH3</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>HFE-365mcf3</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CH2OCH3</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>HFE-374pc2</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>627</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>4,4,4-trifluorobutan-1-ol</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CH2)2CH2OH</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3,4,4,5,5- octafluorocyclopentan-1-ol</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-(CF2)4CH(OH)-)</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>HFE-43-10pccc124</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2OCF2CF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>1870</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>2820</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>HFE-449s1</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>C4F9OCH3</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>HFE-449sl</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>C4F9OCH3</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>n-HFE-7100</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2CF2OCH3</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>n-HFE-7200</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>n-C4F9OC2H5</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>i-HFE-7100</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCF2OCH3</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>HFE-569sf2</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>C4F9OC2H5</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>i-HFE-7200</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>HFE-7300</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCFOC2H5CF2CF2C F3</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>HFE-7500</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>n-C3F7CFOC2H5CF(CF3)2</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236ca12</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>6060</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>HFE-338pcc13</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2CF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>2910</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,3,3,3-hexafluoropropan-2-ol</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOH</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>HG-02</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>CHF2(OCF2CF2)2OCHF2</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="n">
+        <v>2730</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>5730</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>HG-03</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>CHF2(OCF2CF2)3OCHF2</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>5350</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>HG-20</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>HF2C–(OCF2)2–OCF2H</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>HG-21</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>HF2C–OCF2CF2OC- F2OCF2O–CF2H</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="n">
+        <v>3890</v>
+      </c>
+      <c r="F204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>HG-30</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>HF2C–(OCF2)3–OCF2H</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="n">
+        <v>7330</v>
+      </c>
+      <c r="F205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Fluroxene</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCH=CH2</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2-tetrafluoro-1- (fluoromethoxy)ethane</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCF2CF2H</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="F207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>2-ethoxy-3,3,4,4,5- pentafluorotetrahydro-2,5- bis[1,2,2,2-tetrafluoro-1- (trifluoromethyl)ethyl]furan</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>C12H5F19O2</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Difluoro(methoxy)methane</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCHF2</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>HG’-01</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CF2OCH3</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>HG’-02</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>CH3O(CF2CF2O)2CH3</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>HG’-03</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>CH3O(CF2CF2O)3CH3</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>HFE-329me3</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>CF3CFHCF2OCF3</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="n">
+        <v>4550</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,7- undecafluoroheptan-1-ol</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)4CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.533</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,9,9,9- pentadecafluorononan-1-ol</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)6CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="n"/>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,9,9,10,10,11, 11,11-nonadecafluoroundecan-1-ol</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)8CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="n"/>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>2-chloro-1,1,2-trifluoro-1- methoxyethane</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHClF</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n"/>
+      <c r="E217" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>PFPMIE</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>CF3OCF(CF3)CF2OCF2OCF 3</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>9710</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>HFE-216</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>CF3OCF=CF2</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoroethyl formate</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2OCHO</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>2,2,2-trifluoroethyl formate</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCHO</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Formic acid;1,1,1,3,3,3-hexafluoro- propan-2-ol</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCHO</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="n"/>
+      <c r="F222" s="2" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Ethenyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH=CH2</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="n"/>
+      <c r="F223" s="2" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Ethyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH2CH3</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Prop-2-enyl-2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH2CH=CH2</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="n"/>
+      <c r="F225" s="2" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Methyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH3</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3,4,4,4-heptafluorobutan-1-ol</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="n"/>
+      <c r="E227" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2-trifluoro-2-(trifluoromethoxy)- ethane</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CHFOCF3</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>1-ethoxy-1,1,2,3,3,3- hexafluoropropane</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>CF3CHFCF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,2,2,3,3-heptafluoro-3-(1,2,2,2- tetrafluoroethoxy)propane</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2OCHFCF3</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n">
+        <v>6490</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>6630</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3-tetrafluoropropan-1-ol</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,4,4,4-hexafluorobutan-1-ol</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>CF3CHFCF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2-tetrafluoro-3- methoxypropane</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2CH2OCH3</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="n"/>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,2,2,4,5,5,5-nonafluoro-4- (trifluoromethyl)pentan-3-one</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2COCF(CF3)2</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="n"/>
+      <c r="E234" s="2" t="n"/>
+      <c r="F234" s="2" t="n">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>1-ethoxy-1,1,2,2,3,3,3- heptafluoropropane</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Fluoro(methoxy)methane</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCH2F</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Fluoro(fluoromethoxy)methane</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCH2F</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="n"/>
+      <c r="E237" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Difluoro(fluoromethoxy)methane</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCHF2</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="n"/>
+      <c r="E238" s="2" t="n">
+        <v>617</v>
+      </c>
+      <c r="F238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoro(fluoromethoxy)methane</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCF3</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="n"/>
+      <c r="E239" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="F239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoromethyl formate</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCF3</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="n"/>
+      <c r="E240" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="F240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoropropyl formate</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="F241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorobutyl formate</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCF2CF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="F242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoropropyl formate</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCH2CH2CF3</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>1,2,2,2-tetrafluoroethyl formate</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCHFCF3</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="n"/>
+      <c r="E244" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="F244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,3,3,3-hexafluoropropan-2-yl formate</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCH(CF3)2</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="n"/>
+      <c r="E245" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="F245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorobutyl acetate</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF2CF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoropropyl acetate</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="n"/>
+      <c r="E247" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoroethyl acetate</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF2CF3</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoromethyl acetate</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF3</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="n"/>
+      <c r="E249" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Methyl carbonofluoridate</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>FCOOCH3</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="n"/>
+      <c r="E250" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>1,1-difluoroethyl carbonofluoridate</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>FCOOCF2CH3</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="n"/>
+      <c r="E251" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>1,1-difluoroethyl 2,2,2- trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCF2CH3</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="n"/>
+      <c r="E252" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>2,2,2-trifluoroethyl 2,2,2- trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH2CF3</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="n"/>
+      <c r="E253" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Methyl 2,2-difluoroacetate</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>HCF2COOCH3</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="n"/>
+      <c r="E254" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Difluoromethyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCHF2</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="n"/>
+      <c r="E255" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoro-2-methyl-3-pentanone</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2C(O)CF(CF3)2</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="n"/>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>1,1’-Oxybis[2-(difluoromethoxy)- 1,1,2,2-tetrafluoroethane</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>HCF2O(CF2CF2O)2CF2H</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="n"/>
+      <c r="E257" s="2" t="n">
+        <v>4920</v>
+      </c>
+      <c r="F257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>1,1,3,3,4,4,6,6,7,7,9,9,10,10,12,12- hexa-decafluoro-2,5,8,11- Tetraoxadodecane</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>HCF2O(CF2CF2O)3CF2H</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="n"/>
+      <c r="E258" s="2" t="n">
+        <v>4490</v>
+      </c>
+      <c r="F258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>1,1,3,3,4,4,6,6,7,7,9,9,10,10,12,12, 13,13,15,15-eicosafluoro- 2,5,8,11,14-pentaoxapentadecane</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>HCF2O(CF2CF2O)4CF2H</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="n"/>
+      <c r="E259" s="2" t="n">
+        <v>3630</v>
+      </c>
+      <c r="F259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoropropanal</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2CHO</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="n"/>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>2-fluoroethanol</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>CH2FCH2OH</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="n"/>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>2,2-difluoroethanol</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="n"/>
+      <c r="E262" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>2,2,2-trifluoroethanol</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OH</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="n"/>
+      <c r="E263" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>HG-04</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>CHF2O(CF2CF2O)4CHF2</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="n"/>
+      <c r="E264" s="2" t="n"/>
+      <c r="F264" s="2" t="n">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Methyl-perfluoro-heptene-ethers</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>CH3OC7F13</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="n"/>
+      <c r="E265" s="2" t="n"/>
+      <c r="F265" s="2" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1-trifluoro-propan-2-one</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>CF3COCH3</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" s="2" t="n"/>
+      <c r="F266" s="2" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1-trifluoro-butan-2-one</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>CF3COCH2CH3</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" s="2" t="n"/>
+      <c r="F267" s="2" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>1-chloro-2-ethen-oxyethane</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>ClCH2CH2OCH=CH2</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="n"/>
+      <c r="E268" s="2" t="n"/>
+      <c r="F268" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-oxolane</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>c-C4F8O</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="n"/>
+      <c r="E269" s="2" t="n"/>
+      <c r="F269" s="2" t="n">
+        <v>13900</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/client/public/gwp-ar6-reference.xlsx
+++ b/client/public/gwp-ar6-reference.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GWP-100 (AR4-AR6)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GWP-100 (AR4-AR6)'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'GWP-100 (AR4-AR6)'!$A$1:$F$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -438,16 +438,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IPCC AR6 Global Warming Potential (GWP-100) Reference</t>
+          <t>IPCC AR6 Global Warming Potential (GWP-100) Reference -- Full Set (verified against live source PDF, session of 2026-07-25)</t>
         </is>
       </c>
     </row>
@@ -488,76 +488,80 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Scope of this file: the gases actually used in corporate GHG reporting -- CO2, CH4, N2O, SF6, NF3,</t>
+          <t>266 gases: all Major Greenhouse Gases, Hydrofluorocarbons, Fully Fluorinated Species (PFCs),</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>every standard refrigerant HFC, and every standard PFC. Hand-verified against the official PDF.</t>
+          <t>and the full Annex 1 list (Chlorofluorocarbons, Hydrochlorofluorocarbons, Chlorocarbons, Bromocarbons/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Halons, and Halogenated Alcohols/Ethers/Furans/Aldehydes/Ketones).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>NOT included: CFCs, HCFCs, halons, and exotic industrial solvents/foam-blowing-agent chemicals</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>listed in Annex 1 of the source document (roughly 230 additional, mostly obsolete-under-the-</t>
+          <t>Extraction method: this PDF's table has inconsistent column alignment between its header row and data</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Montreal-Protocol or highly specialized substances). If you need one of those, get the value</t>
+          <t>rows (a source-document formatting quirk, not an error in this file). A first extraction attempt using</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>directly from the official PDF linked above rather than assuming it matches this file's format.</t>
+          <t>standard PDF table-grid detection was found to silently misattribute values on ~45% of rows before</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>being caught and discarded. This file was built using position-based extraction (matching each value to</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Methane note: AR6 gives two different values depending on source. Use 'fossil' for fugitive</t>
+          <t>its actual pixel column against the AR4/AR5/AR6 header positions) plus validation against the source</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>emissions from oil/gas/coal and industrial processes; use 'non-fossil' for combustion emissions</t>
+          <t>document's rendered pages. If you spot a value that looks wrong, check it against the official PDF</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>and biogenic sources (landfill, agriculture, wastewater). See the official PDF's 'Methane GWP</t>
+          <t>linked above and report it -- treat this as a well-verified convenience copy, not a substitute for the</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Instructions' box for the full explanation -- this distinction matters and is easy to get backwards.</t>
+          <t>primary source in a dispute.</t>
         </is>
       </c>
     </row>
@@ -567,14 +571,62 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Blank cells mean the substance was not assessed in that report (e.g. many gases have no AR4 value</t>
+          <t>Blank cells mean the substance was not assessed in that IPCC report.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>because they weren't in scope of the Fourth Assessment Report).</t>
+          <t>Values shown as '&lt;1' or '&gt;N' are reproduced as published (IPCC did not give a precise figure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Methane note: AR6 gives two different values. Use 'fossil' for fugitive emissions from oil/gas/coal and</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>industrial processes; use 'non-fossil' for combustion emissions and biogenic sources (landfill,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>agriculture, wastewater). See the official PDF's 'Methane GWP Instructions' box for the full explanation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Category column is derived from each substance's chemical formula pattern (presence of Cl, Br, H, ether</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>linkages), not transcribed section-by-section from the source PDF -- useful for filtering, not a formal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>IUPAC classification.</t>
         </is>
       </c>
     </row>
@@ -589,12 +641,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -666,7 +718,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Methane - non-fossil</t>
+          <t>Methane – non-fossil</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -692,7 +744,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Methane - fossil</t>
+          <t>Methane – fossil</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1451,261 +1503,5627 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PFC-14</t>
+          <t>HFO-1123</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CF4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>7390</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>6630</v>
-      </c>
+          <t>CHF=CF2</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n">
-        <v>7380</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PFC-116</t>
+          <t>HFO-1132a a</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>C2F6</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>12200</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>11100</v>
+          <t>CH2=CF2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>12400</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PFC-218</t>
+          <t>HFO-1141 a</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>C3F8</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>8830</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>8900</v>
+          <t>CH2=CHF</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>9290</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PFC-C-318 (PFC-318)</t>
+          <t>HFO-1225ye(Z) a</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>cyc(-CF2CF2CF2CF2-)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>10300</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>9540</v>
+          <t>(Z)-CF3CF=CHF</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>10200</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PFC-31-10</t>
+          <t>HFO-1225ye(E) a</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>n-C4F10</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n">
-        <v>8860</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>9200</v>
+          <t>(E)-CF3CF=CHF</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>10000</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PFC-41-12</t>
+          <t>HFO-1234ze(Z) a</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>n-C5F12</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>9160</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>8550</v>
+          <t>(Z)-CF3CH=CHF</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>9220</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PFC-51-14</t>
+          <t>HFO-1234ze(E) a</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>n-C6F14</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>9300</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>7910</v>
+          <t>(E)-CF3CH=CHF</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>8620</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PFC-61-16</t>
+          <t>HFO-1234yf a</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>n-C7F16</t>
+          <t>CF3CF=CH2</t>
         </is>
       </c>
       <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n">
-        <v>7820</v>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>8410</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PFC-71-18</t>
+          <t>HFO-1336mzz(E)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>n-C8F18</t>
+          <t>(E)-CF3CH=CHCF3</t>
         </is>
       </c>
       <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n">
-        <v>7620</v>
-      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n">
-        <v>8260</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Fully Fluorinated Species (PFCs)</t>
+          <t>Hydrofluorocarbons</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PFC-91-18</t>
+          <t>HFO-1336mzz(Z)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>(Z)-CF3CH=CHCF3</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1243zf</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH=CH2</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0.261</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1345zfc a</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CH=CH2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>0.182</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,6-nonafluorohex-1- ene</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>n-C4F9CH=CH2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0.204</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,8- tridecafluorooct-1-ene</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>n-C6F13CH=CH2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,9,9,10,10,10- heptadecafluorodec-1-ene</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>n-C8F17CH=CH2</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoro-2-(trifluoromethyl) prop-1-ene</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2C=CH2</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n">
+        <v>0.377</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3-hexafluorocyclopentane</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF2CF2CF2CH2CH2-)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3,4- heptafluorocyclopentane</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF2CF2CF2CHFCH2-)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1,3,3,4,4,5,5-heptafluoro- cyclopentene</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF2CF2CF2CF=CH-)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>(4s,5s)-1,1,2,2,3,3,4,5- octafluorocyclopentane</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>trans-cyc (- CF2CF2CF2CHFCHF-)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1438ezy(E)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>(E)-(CF3)2CFCH=CHF</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n">
+        <v>8.220000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>HFO-1447fz</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)2CH=CH2</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1,3,3,4,4-pentafluorocyclobutene</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CH=CFCF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4-tetrafluorocyclobutene</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CH=CHCF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>PFC-14</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>CF4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>7390</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>6630</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>7380</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>PFC-116</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>C2F6</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>12200</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>PFC-218</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>C3F8</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>8830</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>8900</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>9290</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>PFC-c216</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>c-C3F6</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>&gt;17340</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>PFC-C-318 (PFC-318) b</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CF2CF2CF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>9540</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>PFC-31-10 c</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>n-C4F10</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>8860</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>9200</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>PFC-41-12 c</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>n-C5F12</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>9160</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>8550</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>9220</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>PFC-51-14 c</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>n-C6F14</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>9300</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>7910</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>8620</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>PFC-61-16</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>n-C7F16</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n">
+        <v>7820</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>8410</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>PFC-71-18</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>n-C8F18</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n">
+        <v>7620</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>8260</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>PFC-91-18 c</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
           <t>C10F18</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E43" s="2" t="n">
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>&gt;7500</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
         <v>7190</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F68" s="2" t="n">
         <v>7480</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>PFC-1114</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>CF2=CF2</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>PFC-1216</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF=CF2</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Pentadecafluorotriethylamine</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>N(C2F5)3</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorotripropylamine</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>N(CF2CF2CF3)3</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n">
+        <v>9030</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Heptacosafluorotributylamine</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>N(CF2CF2CF2CF3)3</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n">
+        <v>8490</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorotripentylamine</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>N(CF2CF2CF2CF2CF3)3</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n">
+        <v>7260</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Heptafluoroisobutyronitrile</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCN</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoromethylsulfur pentafluoride</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>SF5CF3</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>17700</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Sulfuryl fluoride</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>SO2F2</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n">
+        <v>4090</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Hexafluoro-cyclobutene</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-CF=CFCF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-cyclopentene (Perfluorocyclopentene)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>cyc (- CF=CFCF2CF2CF2-)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>78.09999999999999</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3,4,4,4a,5,5,6,6,7,7,8,8,8a- octadecafluoronaphthalene (Perfluorodecalin (cis))</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>(Z)-C10F18</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n">
+        <v>7240</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2,3,3,4,4,4a,5,5,6,6,7,7,8,8,8a- octadecafluoronaphthalene (Perfluorodecalin (trans))</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>(E)-C10F18</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n">
+        <v>6290</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>7120</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,3,4,4-hexafluorobuta-1,3-diene</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>CF2=CFCF=CF2</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-1-butene</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF=CF2</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-2-butene</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF=CFCF3</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>CFC-11</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>CCl3F</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CFC-12</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>CCl2F2</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10900</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>10200</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>CFC-13</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>CClF3</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>13900</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>CFC-112</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>CCl2FCCl2F</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>CFC-112a</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>CCl3CClF2</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n">
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CFC-113</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>CCl2FCClF2</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>6130</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>5820</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>6520</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>CFC-113a</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>CCl3CF3</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>CFC-114</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>CClF2CClF2</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>8590</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>9430</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>CFC-114a</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>CCl2FCF3</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n">
+        <v>7420</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>CFC-115</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>CClF2CF3</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>7370</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>E-R316c</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>trans cyc (- CClFCF2CF2CClF-)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Z-R316c</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>cis cyc (-CClFCF2CF2CClF- )</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n">
+        <v>5660</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>CFC 1112</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>CClF=CClF</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>CFC 1112a</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>CCl2=CF2</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-21</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2F</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-22</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>CHClF2</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1810</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1760</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-31</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClF</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n">
+        <v>79.40000000000001</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-121</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CCl2F</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-122</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CClF2</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-122a</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCCl2F</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-123</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CF3</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-123a</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCClF2</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n">
+        <v>370</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-124</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCF3</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>609</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>527</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-124a</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CClF2</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-132</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCHClF</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-132a</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CHF2</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-132c</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>CH2FCCl2F</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-133a</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClCF3</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-141</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClCHClF</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-141b</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>CH3CCl2F</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>725</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-142b</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>CH3CClF2</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-225ca</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>CHCl2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>HCFC-225cb</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>CHClFCF2CClF2</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>595</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>HCFO-1233zd(E)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>(E)-CF3CH=CHCl</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>HCFO-1233zd(Z)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>(Z)-CF3CH=CHCl</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n">
+        <v>0.454</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>(e)-1-chloro-2-fluoroethene</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>(E/Z)-CHCl=CHF</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>(E)-1-chloro-3,3,3-trifluoroprop-1- ene</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>trans-CF3CH=CHCl</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Methyl chloroform</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>CH3CCl3</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Carbon tetrachloride</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>CCl4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Methyl chloride</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>CH3Cl</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Methylene chloride</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>CH2Cl2</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Chloroform</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>CHCl3</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Chloroethane</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>CH3CH2Cl</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n">
+        <v>0.481</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>1,2-dichloroethane</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>CH2ClCH2Cl</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2-trichloroethene</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>CHCl=CCl2</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Chlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2-tetrachloroethene</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>CCl2=CCl2</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2-chloropropane</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>CH3CHClCH3</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>1-chlorobutane</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>CH3(CH2)2CH2Cl</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Methyl bromide</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>CH3Br</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Methylene bromide</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>CH2Br2</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1201</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>CHBrF2</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1202</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>CBr2F2</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1211</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>CBrClF2</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1301</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>CBrF3</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>7140</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>6290</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2301</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>CH2BrCF3</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2311</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>CHBrClCF3</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2401</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>CHBrFCF3</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Halon-2402</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>CBrF2CBrF2</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1640</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Tribromomethane</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>CHBr3</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Halon-1011</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>CH2BrCl</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Bromoethane</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>CH3CH2Br</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n">
+        <v>0.487</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>1,2-dibromoethane</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>CH2BrCH2Br</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>1-bromopropane</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>CH3CH2CH2Br</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Bromocarbons, Hydrobromocarbons and Halons</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2-bromopropane</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>CH3CHBrCH3</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>HFE-125</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF3</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>14900</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>HFE-134</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>6320</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>5560</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>6630</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>HFE-143a</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF3</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>756</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>523</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>HFE-227ea</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>CF3CHFOCF3</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>HCFE-235ca2</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2CHFCl</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n">
+        <v>583</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>HCFE-235da2</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCHClCF3</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>491</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236ea2</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCHFCF3</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236fa</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCF3</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>HFE-245cb2</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2OCH3</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>654</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>HFE-245fa1</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OCF3</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>828</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>HFE-245fa2</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCH2CF3</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>659</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>812</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3,3-pentafluoropropan-1-ol</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>HFE-254cb1</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>HFE-254cb2</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236ca</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n">
+        <v>4240</v>
+      </c>
+      <c r="F163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>HFE-263mf (HFE-263fb2)</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCH3</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>HFE-263m1</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>CF3OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>HFE-365mcf2</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="F166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoropropan-1-ol</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>HFE-329mcc2</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2OCF2CF3</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>919</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>HFE-338mmz1</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCHF2</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>HFE-338mcf2</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCF2CF3</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>552</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>929</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mmz1</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCH2F</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mcc3</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>530</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mcf2</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OCF2CF3</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>374</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347pcf2</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2OCH2CF3</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>HFE-347mmy1</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFOCH3</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>363</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356mec3</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHFCF3</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>387</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356mff2</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCH2CF3</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356pcf2</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OCF2CHF2</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>719</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356pcf3</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCH2CF2CHF2</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>502</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356pcc3</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CF2CHF2</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>HFE-356mmz1</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCH3</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>HFE-365mcf3</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CH2OCH3</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>HFE-374pc2</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>557</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>627</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>4,4,4-trifluorobutan-1-ol</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CH2)2CH2OH</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3,4,4,5,5- octafluorocyclopentan-1-ol</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>cyc (-(CF2)4CH(OH)-)</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>HFE-43-10pccc124</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2OCF2CF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>1870</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>2820</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>HFE-449s1</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>C4F9OCH3</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>HFE-449sl</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>C4F9OCH3</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>n-HFE-7100</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2CF2OCH3</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>n-HFE-7200</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>n-C4F9OC2H5</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="F190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>i-HFE-7100</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCF2OCH3</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n">
+        <v>407</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>HFE-569sf2</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>C4F9OC2H5</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>i-HFE-7200</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>34.3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>HFE-7300</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CFCFOC2H5CF2CF2C F3</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>HFE-7500</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>n-C3F7CFOC2H5CF(CF3)2</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>HFE-236ca12</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>6060</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>HFE-338pcc13</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>CHF2OCF2CF2OCHF2</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>2910</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,3,3,3-hexafluoropropan-2-ol</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOH</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>HG-02</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>CHF2(OCF2CF2)2OCHF2</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n">
+        <v>2730</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>5730</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>HG-03</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>CHF2(OCF2CF2)3OCHF2</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>5350</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>HG-20</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>HF2C–(OCF2)2–OCF2H</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>HG-21</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>HF2C–OCF2CF2OC- F2OCF2O–CF2H</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="n">
+        <v>3890</v>
+      </c>
+      <c r="F202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>HG-30</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>HF2C–(OCF2)3–OCF2H</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="n">
+        <v>7330</v>
+      </c>
+      <c r="F203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Fluroxene</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCH=CH2</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>0.058</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2-tetrafluoro-1- (fluoromethoxy)ethane</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCF2CF2H</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="F205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>2-ethoxy-3,3,4,4,5- pentafluorotetrahydro-2,5- bis[1,2,2,2-tetrafluoro-1- (trifluoromethyl)ethyl]furan</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>C12H5F19O2</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Difluoro(methoxy)methane</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCHF2</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>HG’-01</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CF2OCH3</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>HG’-02</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>CH3O(CF2CF2O)2CH3</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>HG’-03</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>CH3O(CF2CF2O)3CH3</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>HFE-329me3</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>CF3CFHCF2OCF3</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="n">
+        <v>4550</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,7- undecafluoroheptan-1-ol</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)4CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>0.533</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,9,9,9- pentadecafluorononan-1-ol</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)6CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>3,3,4,4,5,5,6,6,7,7,8,8,9,9,10,10,11, 11,11-nonadecafluoroundecan-1-ol</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>CF3(CF2)8CH2CH2OH</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>0.273</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>2-chloro-1,1,2-trifluoro-1- methoxyethane</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCF2CHClF</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="n"/>
+      <c r="E215" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>PFPMIE</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>CF3OCF(CF3)CF2OCF2OCF 3</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>9710</v>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>HFE-216</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>CF3OCF=CF2</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="n"/>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoroethyl formate</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2OCHO</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="n"/>
+      <c r="E218" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>2,2,2-trifluoroethyl formate</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OCHO</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>54.8</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Formic acid;1,1,1,3,3,3-hexafluoro- propan-2-ol</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>(CF3)2CHOCHO</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="n"/>
+      <c r="F220" s="2" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Ethenyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH=CH2</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="n"/>
+      <c r="F221" s="2" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Ethyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH2CH3</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Prop-2-enyl-2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH2CH=CH2</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="n"/>
+      <c r="F223" s="2" t="n">
+        <v>0.007</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Methyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH3</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3,4,4,4-heptafluorobutan-1-ol</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2-trifluoro-2-(trifluoromethoxy)- ethane</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CHFOCF3</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>1-ethoxy-1,1,2,3,3,3- hexafluoropropane</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>CF3CHFCF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="n"/>
+      <c r="E227" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,2,2,3,3-heptafluoro-3-(1,2,2,2- tetrafluoroethoxy)propane</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2OCHFCF3</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="n">
+        <v>6490</v>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>6630</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,3-tetrafluoropropan-1-ol</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>2,2,3,4,4,4-hexafluorobutan-1-ol</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>CF3CHFCF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>1,1,2,2-tetrafluoro-3- methoxypropane</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CF2CH2OCH3</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,2,2,4,5,5,5-nonafluoro-4- (trifluoromethyl)pentan-3-one</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2COCF(CF3)2</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="n"/>
+      <c r="F232" s="2" t="n">
+        <v>0.114</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>1-ethoxy-1,1,2,2,3,3,3- heptafluoropropane</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2CF2OCH2CH3</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="n"/>
+      <c r="E233" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Fluoro(methoxy)methane</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>CH3OCH2F</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="n"/>
+      <c r="E234" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Fluoro(fluoromethoxy)methane</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCH2F</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Difluoro(fluoromethoxy)methane</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCHF2</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n">
+        <v>617</v>
+      </c>
+      <c r="F236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoro(fluoromethoxy)methane</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>CH2FOCF3</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="n"/>
+      <c r="E237" s="2" t="n">
+        <v>751</v>
+      </c>
+      <c r="F237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoromethyl formate</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCF3</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="n"/>
+      <c r="E238" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="F238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoropropyl formate</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="n"/>
+      <c r="E239" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="F239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorobutyl formate</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCF2CF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="n"/>
+      <c r="E240" s="2" t="n">
+        <v>392</v>
+      </c>
+      <c r="F240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoropropyl formate</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCH2CH2CF3</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>1,2,2,2-tetrafluoroethyl formate</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCHFCF3</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="F242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1,3,3,3-hexafluoropropan-2-yl formate</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>HCOOCH(CF3)2</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="n">
+        <v>333</v>
+      </c>
+      <c r="F243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Perfluorobutyl acetate</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF2CF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="n"/>
+      <c r="E244" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoropropyl acetate</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF2CF2CF3</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="n"/>
+      <c r="E245" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoroethyl acetate</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF2CF3</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Trifluoromethyl acetate</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>CH3COOCF3</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="n"/>
+      <c r="E247" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Methyl carbonofluoridate</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>FCOOCH3</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>1,1-difluoroethyl carbonofluoridate</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>FCOOCF2CH3</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="n"/>
+      <c r="E249" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>1,1-difluoroethyl 2,2,2- trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCF2CH3</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="n"/>
+      <c r="E250" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>2,2,2-trifluoroethyl 2,2,2- trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCH2CF3</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="n"/>
+      <c r="E251" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Methyl 2,2-difluoroacetate</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>HCF2COOCH3</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="n"/>
+      <c r="E252" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Difluoromethyl 2,2,2-trifluoroacetate</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>CF3COOCHF2</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="n"/>
+      <c r="E253" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Perfluoro-2-methyl-3-pentanone</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>CF3CF2C(O)CF(CF3)2</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="n"/>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>1,1’-Oxybis[2-(difluoromethoxy)- 1,1,2,2-tetrafluoroethane</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>HCF2O(CF2CF2O)2CF2H</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="n"/>
+      <c r="E255" s="2" t="n">
+        <v>4920</v>
+      </c>
+      <c r="F255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>1,1,3,3,4,4,6,6,7,7,9,9,10,10,12,12- hexa-decafluoro-2,5,8,11- Tetraoxadodecane</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>HCF2O(CF2CF2O)3CF2H</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="n"/>
+      <c r="E256" s="2" t="n">
+        <v>4490</v>
+      </c>
+      <c r="F256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>1,1,3,3,4,4,6,6,7,7,9,9,10,10,12,12, 13,13,15,15-eicosafluoro- 2,5,8,11,14-pentaoxapentadecane</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>HCF2O(CF2CF2O)4CF2H</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="n"/>
+      <c r="E257" s="2" t="n">
+        <v>3630</v>
+      </c>
+      <c r="F257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>3,3,3-trifluoropropanal</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2CHO</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="n"/>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>2-fluoroethanol</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>CH2FCH2OH</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="n"/>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>2,2-difluoroethanol</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>CHF2CH2OH</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="n"/>
+      <c r="E260" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>2,2,2-trifluoroethanol</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>CF3CH2OH</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="n"/>
+      <c r="E261" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Hydrofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>HG-04</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>CHF2O(CF2CF2O)4CHF2</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="n"/>
+      <c r="E262" s="2" t="n"/>
+      <c r="F262" s="2" t="n">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Methyl-perfluoro-heptene-ethers</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>CH3OC7F13</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="n"/>
+      <c r="E263" s="2" t="n"/>
+      <c r="F263" s="2" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1-trifluoro-propan-2-one</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>CF3COCH3</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="n"/>
+      <c r="E264" s="2" t="n"/>
+      <c r="F264" s="2" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Halogenated Alcohols, Ethers, Furans, Aldehydes and Ketones</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>1,1,1-trifluoro-butan-2-one</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>CF3COCH2CH3</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="n"/>
+      <c r="E265" s="2" t="n"/>
+      <c r="F265" s="2" t="n">
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Hydrochlorofluorocarbons</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>1-chloro-2-ethen-oxyethane</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>ClCH2CH2OCH=CH2</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" s="2" t="n"/>
+      <c r="F266" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Other / Fully Fluorinated Species</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Octafluoro-oxolane</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>c-C4F8O</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" s="2" t="n"/>
+      <c r="F267" s="2" t="n">
+        <v>13900</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F269"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>